--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-13T00:32:12+00:00</t>
+          <t>2026-09-14T00:34:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-14T00:34:49+00:00</t>
+          <t>2026-09-15T01:08:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-15T01:08:11+00:00</t>
+          <t>2026-09-16T00:56:15+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-16T00:56:15+00:00</t>
+          <t>2026-09-17T02:25:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-17T02:25:49+00:00</t>
+          <t>2026-09-18T00:57:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-18T00:57:12+00:00</t>
+          <t>2026-09-19T00:51:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-19T00:51:32+00:00</t>
+          <t>2026-09-20T00:34:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-20T00:34:36+00:00</t>
+          <t>2026-09-21T00:43:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-21T00:43:59+00:00</t>
+          <t>2026-09-22T01:26:03+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-22T01:26:03+00:00</t>
+          <t>2026-09-23T01:07:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-23T01:07:41+00:00</t>
+          <t>2026-09-24T01:03:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-24T01:03:32+00:00</t>
+          <t>2026-09-25T01:05:16+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-25T01:05:16+00:00</t>
+          <t>2026-09-26T01:07:00+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-26T01:07:00+00:00</t>
+          <t>2026-09-27T01:04:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-27T01:04:27+00:00</t>
+          <t>2026-09-28T01:23:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-28T01:23:18+00:00</t>
+          <t>2026-09-29T02:28:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-29T02:28:07+00:00</t>
+          <t>2026-09-30T01:47:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-30T01:47:18+00:00</t>
+          <t>2026-10-01T01:45:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-01T01:45:42+00:00</t>
+          <t>2026-10-02T01:55:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-02T01:55:45+00:00</t>
+          <t>2026-10-03T01:38:46+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-03T01:38:46+00:00</t>
+          <t>2026-10-04T02:19:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-04T02:19:14+00:00</t>
+          <t>2026-10-05T01:27:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-05T01:27:45+00:00</t>
+          <t>2026-10-06T02:38:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-06T02:38:31+00:00</t>
+          <t>2026-10-07T01:56:50+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-07T01:56:50+00:00</t>
+          <t>2026-10-08T02:24:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-08T02:24:56+00:00</t>
+          <t>2026-10-09T02:43:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-09T02:43:18+00:00</t>
+          <t>2026-10-10T02:02:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T02:02:45+00:00</t>
+          <t>2026-10-10T09:17:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T09:17:27+00:00</t>
+          <t>2026-10-10T16:05:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T16:05:07+00:00</t>
+          <t>2026-10-10T22:09:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-10T22:09:54+00:00</t>
+          <t>2026-10-11T01:27:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T01:27:45+00:00</t>
+          <t>2026-10-11T09:34:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T09:34:34+00:00</t>
+          <t>2026-10-11T16:31:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T16:31:01+00:00</t>
+          <t>2026-10-11T22:38:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-11T22:38:38+00:00</t>
+          <t>2026-10-12T01:58:13+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T01:58:13+00:00</t>
+          <t>2026-10-12T10:04:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T10:04:36+00:00</t>
+          <t>2026-10-12T20:06:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-12T20:06:30+00:00</t>
+          <t>2026-10-13T03:19:58+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T03:19:58+00:00</t>
+          <t>2026-10-13T14:45:02+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T14:45:02+00:00</t>
+          <t>2026-10-13T20:30:12+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-13T20:30:12+00:00</t>
+          <t>2026-10-14T01:32:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T01:32:37+00:00</t>
+          <t>2026-10-14T08:17:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T08:17:18+00:00</t>
+          <t>2026-10-14T15:41:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T15:41:24+00:00</t>
+          <t>2026-10-14T22:01:56+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-14T22:01:56+00:00</t>
+          <t>2026-10-15T01:10:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T01:10:39+00:00</t>
+          <t>2026-10-15T07:54:55+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T07:54:55+00:00</t>
+          <t>2026-10-15T15:27:47+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T15:27:47+00:00</t>
+          <t>2026-10-15T21:55:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-15T21:55:34+00:00</t>
+          <t>2026-10-16T00:57:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T00:57:21+00:00</t>
+          <t>2026-10-16T07:46:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T07:46:24+00:00</t>
+          <t>2026-10-16T15:07:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T15:07:27+00:00</t>
+          <t>2026-10-16T21:53:29+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-16T21:53:29+00:00</t>
+          <t>2026-10-17T00:57:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T00:57:31+00:00</t>
+          <t>2026-10-17T07:23:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T07:23:43+00:00</t>
+          <t>2026-10-17T14:03:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T14:03:51+00:00</t>
+          <t>2026-10-17T17:43:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T17:43:24+00:00</t>
+          <t>2026-10-17T21:12:17+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-17T21:12:17+00:00</t>
+          <t>2026-10-18T00:32:49+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T00:32:49+00:00</t>
+          <t>2026-10-18T07:37:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T07:37:51+00:00</t>
+          <t>2026-10-18T14:15:52+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T14:15:52+00:00</t>
+          <t>2026-10-18T17:44:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T17:44:11+00:00</t>
+          <t>2026-10-18T21:14:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-18T21:14:19+00:00</t>
+          <t>2026-10-19T00:39:54+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T00:39:54+00:00</t>
+          <t>2026-10-19T08:21:44+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T08:21:44+00:00</t>
+          <t>2026-10-19T17:19:10+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T17:19:10+00:00</t>
+          <t>2026-10-19T22:44:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-19T22:44:31+00:00</t>
+          <t>2026-10-20T01:24:45+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T01:24:45+00:00</t>
+          <t>2026-10-20T08:05:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T08:05:53+00:00</t>
+          <t>2026-10-20T15:32:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T15:32:09+00:00</t>
+          <t>2026-10-20T22:02:31+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-20T22:02:31+00:00</t>
+          <t>2026-10-21T01:11:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T01:11:26+00:00</t>
+          <t>2026-10-21T08:11:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T08:11:14+00:00</t>
+          <t>2026-10-21T15:48:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T15:48:05+00:00</t>
+          <t>2026-10-21T22:05:09+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-21T22:05:09+00:00</t>
+          <t>2026-10-22T01:08:21+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T01:08:21+00:00</t>
+          <t>2026-10-22T08:11:25+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T08:11:25+00:00</t>
+          <t>2026-10-22T15:47:14+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T15:47:14+00:00</t>
+          <t>2026-10-22T22:02:26+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-22T22:02:26+00:00</t>
+          <t>2026-10-23T01:09:07+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T01:09:07+00:00</t>
+          <t>2026-10-23T08:10:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T08:10:04+00:00</t>
+          <t>2026-10-23T15:35:18+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T15:35:18+00:00</t>
+          <t>2026-10-23T21:50:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-23T21:50:05+00:00</t>
+          <t>2026-10-24T01:18:11+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T01:18:11+00:00</t>
+          <t>2026-10-24T07:48:37+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T07:48:37+00:00</t>
+          <t>2026-10-24T09:10:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T09:10:30+00:00</t>
+          <t>2026-10-24T14:13:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T14:13:01+00:00</t>
+          <t>2026-10-24T15:23:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T15:23:41+00:00</t>
+          <t>2026-10-24T17:45:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T17:45:04+00:00</t>
+          <t>2026-10-24T21:21:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-24T21:21:42+00:00</t>
+          <t>2026-10-25T00:43:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T00:43:30+00:00</t>
+          <t>2026-10-25T07:58:20+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T07:58:20+00:00</t>
+          <t>2026-10-25T14:43:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T14:43:32+00:00</t>
+          <t>2026-10-25T18:01:24+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T18:01:24+00:00</t>
+          <t>2026-10-25T21:26:30+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-25T21:26:30+00:00</t>
+          <t>2026-10-26T00:57:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T00:57:48+00:00</t>
+          <t>2026-10-26T08:29:42+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T08:29:42+00:00</t>
+          <t>2026-10-26T17:05:53+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T17:05:53+00:00</t>
+          <t>2026-10-26T22:58:43+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-26T22:58:43+00:00</t>
+          <t>2026-10-27T01:45:32+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:45:32+00:00</t>
+          <t>2026-10-27T01:48:38+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T01:48:38+00:00</t>
+          <t>2026-10-27T08:32:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T08:32:34+00:00</t>
+          <t>2026-10-27T16:08:51+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T16:08:51+00:00</t>
+          <t>2026-10-27T22:47:39+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-27T22:47:39+00:00</t>
+          <t>2026-10-28T01:56:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T01:56:59+00:00</t>
+          <t>2026-10-28T09:12:05+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T09:12:05+00:00</t>
+          <t>2026-10-28T16:56:34+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T16:56:34+00:00</t>
+          <t>2026-10-28T22:56:22+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-28T22:56:22+00:00</t>
+          <t>2026-10-29T02:01:48+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T02:01:48+00:00</t>
+          <t>2026-10-29T06:41:59+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T06:41:59+00:00</t>
+          <t>2026-10-29T09:10:04+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T09:10:04+00:00</t>
+          <t>2026-10-29T17:14:06+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T17:14:06+00:00</t>
+          <t>2026-10-29T23:04:27+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-29T23:04:27+00:00</t>
+          <t>2026-10-30T02:17:41+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T02:17:41+00:00</t>
+          <t>2026-10-30T09:21:01+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T09:21:01+00:00</t>
+          <t>2026-10-30T16:55:19+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T16:55:19+00:00</t>
+          <t>2026-10-30T22:45:36+00:00</t>
         </is>
       </c>
     </row>

--- a/public/downloads/eu-offshore-centres.xlsx
+++ b/public/downloads/eu-offshore-centres.xlsx
@@ -511,7 +511,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-10-30T22:45:36+00:00</t>
+          <t>2026-10-31T01:56:53+00:00</t>
         </is>
       </c>
     </row>
